--- a/ValidationReports/Configurations/Plots.xlsx
+++ b/ValidationReports/Configurations/Plots.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub repositories\ModelReporitory\Pregnancy-Models\ValidadionReports\Configurations\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub repositories\ModelReporitory\Pregnancy-Models\ValidationReports\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB9E408-FFF8-4D52-99A7-6565812CD543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68A1F761-F43D-4D6C-984E-067103B0A5F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DataCombined" sheetId="1" r:id="rId1"/>
@@ -654,9 +654,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M21"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="86" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="67.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="86" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -697,7 +710,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -717,7 +730,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -725,7 +738,7 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
         <v>21</v>
@@ -734,7 +747,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -742,7 +755,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F4" t="s">
         <v>22</v>
@@ -751,7 +764,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -759,7 +772,7 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
         <v>23</v>
@@ -768,7 +781,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -776,7 +789,7 @@
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s">
         <v>24</v>
@@ -785,7 +798,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -793,7 +806,7 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
         <v>25</v>
@@ -802,7 +815,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -822,7 +835,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -839,7 +852,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -859,7 +872,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -876,7 +889,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -896,7 +909,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -904,7 +917,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -913,7 +926,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -921,7 +934,7 @@
         <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F14" t="s">
         <v>22</v>
@@ -930,7 +943,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -938,7 +951,7 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F15" t="s">
         <v>23</v>
@@ -947,7 +960,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -955,7 +968,7 @@
         <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F16" t="s">
         <v>24</v>
@@ -964,7 +977,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -972,7 +985,7 @@
         <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F17" t="s">
         <v>25</v>
@@ -981,7 +994,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -1001,7 +1014,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>35</v>
       </c>
@@ -1018,7 +1031,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -1038,7 +1051,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -1063,9 +1076,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N15"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>37</v>
       </c>
@@ -1109,7 +1122,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>50</v>
       </c>
@@ -1129,7 +1142,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>55</v>
       </c>
@@ -1149,7 +1162,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>58</v>
       </c>
@@ -1166,7 +1179,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -1183,7 +1196,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>62</v>
       </c>
@@ -1200,7 +1213,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>64</v>
       </c>
@@ -1217,7 +1230,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -1234,7 +1247,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>68</v>
       </c>
@@ -1254,7 +1267,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>70</v>
       </c>
@@ -1274,7 +1287,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>71</v>
       </c>
@@ -1291,7 +1304,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>72</v>
       </c>
@@ -1308,7 +1321,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>73</v>
       </c>
@@ -1325,7 +1338,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>74</v>
       </c>
@@ -1342,7 +1355,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -1367,9 +1380,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>76</v>
       </c>
@@ -1380,7 +1393,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1388,7 +1401,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>78</v>
       </c>
@@ -1396,7 +1409,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>80</v>
       </c>
@@ -1404,7 +1417,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -1412,7 +1425,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>82</v>
       </c>
@@ -1420,7 +1433,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>84</v>
       </c>
@@ -1436,9 +1449,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>86</v>
       </c>
@@ -1457,19 +1470,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1482,34 +1495,34 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>91</v>
       </c>
